--- a/data_ext/budget_policies.xlsx
+++ b/data_ext/budget_policies.xlsx
@@ -584,6 +584,9 @@
       <c r="D2" t="s">
         <v>5</v>
       </c>
+      <c r="E2">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
@@ -615,6 +618,9 @@
       <c r="D4" t="s">
         <v>8</v>
       </c>
+      <c r="E4">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
@@ -629,6 +635,9 @@
       <c r="D5" t="s">
         <v>42</v>
       </c>
+      <c r="E5">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
@@ -643,6 +652,9 @@
       <c r="D6" t="s">
         <v>11</v>
       </c>
+      <c r="E6">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
@@ -725,6 +737,9 @@
       <c r="D11" t="s">
         <v>46</v>
       </c>
+      <c r="E11">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12">
@@ -824,6 +839,9 @@
       <c r="D17" t="s">
         <v>50</v>
       </c>
+      <c r="E17">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18">
@@ -837,6 +855,9 @@
       </c>
       <c r="D18" t="s">
         <v>51</v>
+      </c>
+      <c r="E18">
+        <v>0.5</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
